--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487870_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487870_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. BURGOS CABALLERO</t>
+          <t>J. JIMÉNEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3038</v>
+        <v>4.5421</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0074</v>
+        <v>2.4994</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2964</v>
+        <v>2.0427</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9446</v>
+        <v>3.3983</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2391</v>
+        <v>0.1089</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7055</v>
+        <v>3.2894</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3896</v>
+        <v>3.3944</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5609</v>
+        <v>-0.0664</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9504</v>
+        <v>3.4608</v>
       </c>
       <c r="M2" t="n">
-        <v>0.555</v>
+        <v>0.0039</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.1753</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2449</v>
+        <v>-0.1714</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6244</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7349</v>
+        <v>0.5383</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6585</v>
+        <v>0.3725</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0764</v>
+        <v>0.1658</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5557</v>
+        <v>4.093</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7831</v>
+        <v>2.9974</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7726</v>
+        <v>1.0956</v>
       </c>
       <c r="G3" t="n">
         <v>2.4867</v>
@@ -688,13 +688,13 @@
         <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1096</v>
+        <v>0.6469</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2577</v>
+        <v>0.472</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1481</v>
+        <v>0.1749</v>
       </c>
       <c r="V3" t="n">
         <v>1.1675</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ GONZÁLEZ</t>
+          <t>A. BURGOS CABALLERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.842</v>
+        <v>3.9318</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8873</v>
+        <v>1.4887</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9546</v>
+        <v>2.4432</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3983</v>
+        <v>1.9446</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1089</v>
+        <v>0.2391</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2894</v>
+        <v>1.7055</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3944</v>
+        <v>1.3896</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0664</v>
+        <v>-0.5609</v>
       </c>
       <c r="L4" t="n">
-        <v>3.4608</v>
+        <v>1.9504</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0039</v>
+        <v>0.555</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1753</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1714</v>
+        <v>-0.2449</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1619</v>
+        <v>1.3629</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2396</v>
+        <v>1.1397</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.2232</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9991</v>
+        <v>2.363</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7246</v>
+        <v>-0.2727</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7237</v>
+        <v>2.6356</v>
       </c>
       <c r="G5" t="n">
         <v>0.9768</v>
@@ -844,13 +844,13 @@
         <v>1.4568</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2264</v>
+        <v>0.1375</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0619</v>
+        <v>0.5139</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2883</v>
+        <v>-0.3764</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>J. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0163</v>
+        <v>0.7373</v>
       </c>
       <c r="E6" t="n">
-        <v>1.684</v>
+        <v>-0.985</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6677</v>
+        <v>1.7224</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5301</v>
+        <v>1.0061</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3027</v>
+        <v>2.0062</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8329</v>
+        <v>-1.0001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2211</v>
+        <v>-0.2021</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7395</v>
+        <v>1.8716</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5184</v>
+        <v>-2.0737</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7512</v>
+        <v>1.2082</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5632</v>
+        <v>0.1346</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3144</v>
+        <v>1.0736</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8731</v>
+        <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4216</v>
+        <v>-0.0169</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8136</v>
+        <v>0.2577</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.392</v>
+        <v>-0.2746</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7076</v>
+        <v>-0.4599</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6899</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3975</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MARIN ORTEGA</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.0273</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1808</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>2.016</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0061</v>
+        <v>-0.5301</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0062</v>
+        <v>1.3027</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0001</v>
+        <v>-1.8329</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2021</v>
+        <v>0.2211</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8716</v>
+        <v>0.7395</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0737</v>
+        <v>-0.5184</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2082</v>
+        <v>-0.7512</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1346</v>
+        <v>0.5632</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0736</v>
+        <v>-1.3144</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2487</v>
+        <v>1.8731</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0809</v>
+        <v>0.4325</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0619</v>
+        <v>0.8539</v>
       </c>
       <c r="U7" t="n">
-        <v>0.019</v>
+        <v>-0.4214</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.4599</v>
+        <v>-0.7076</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6899</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4599</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1066</v>
+        <v>-0.4535</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1108</v>
+        <v>-0.2599</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2174</v>
+        <v>-0.1937</v>
       </c>
       <c r="G8" t="n">
         <v>0.2626</v>
@@ -1078,13 +1078,13 @@
         <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1738</v>
+        <v>1.6137</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7111</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4628</v>
+        <v>1.0517</v>
       </c>
       <c r="V8" t="n">
         <v>0.5838</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5962</v>
+        <v>-1.2873</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0233</v>
+        <v>0.2562</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5729</v>
+        <v>-1.5435</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1562</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0457</v>
+        <v>0.2632</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3915</v>
+        <v>-0.1119</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3458</v>
+        <v>0.3751</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3538</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6572</v>
+        <v>-4.1003</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3337</v>
+        <v>-2.9237</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3234</v>
+        <v>-1.1766</v>
       </c>
       <c r="G10" t="n">
         <v>-3.7516</v>
@@ -1234,13 +1234,13 @@
         <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2812</v>
+        <v>0.2756</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1338</v>
+        <v>0.2763</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1474</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1348</v>
+        <v>-4.3902</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6041</v>
+        <v>-3.7421</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.6481</v>
       </c>
       <c r="G11" t="n">
         <v>-4.5619</v>
@@ -1312,13 +1312,13 @@
         <v>1.0406</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1951</v>
+        <v>0.9396</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5905</v>
+        <v>0.2715</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7856</v>
+        <v>0.6681</v>
       </c>
       <c r="V11" t="n">
         <v>1.5213</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.8111</v>
+        <v>-6.0465</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0048</v>
+        <v>-3.4456</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8063</v>
+        <v>-2.6008</v>
       </c>
       <c r="G12" t="n">
         <v>-4.3609</v>
@@ -1390,13 +1390,13 @@
         <v>0.2081</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4502</v>
+        <v>0.3144</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.0281</v>
       </c>
       <c r="U12" t="n">
-        <v>0.137</v>
+        <v>0.3425</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1675</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.540599999999998</v>
+        <v>-0.5832999999999995</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.6203</v>
+        <v>-3.663</v>
       </c>
       <c r="F13" t="n">
-        <v>3.079700000000001</v>
+        <v>3.079699999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-3.2856</v>
@@ -1468,13 +1468,13 @@
         <v>11.4465</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5505</v>
+        <v>6.507699999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6221</v>
+        <v>4.579499999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9285</v>
+        <v>1.9283</v>
       </c>
       <c r="V13" t="n">
         <v>1.3975</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0508</v>
+        <v>5.2842</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4868</v>
+        <v>1.8082</v>
       </c>
       <c r="F14" t="n">
-        <v>3.564</v>
+        <v>3.4759</v>
       </c>
       <c r="G14" t="n">
         <v>3.1383</v>
@@ -1546,13 +1546,13 @@
         <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9407</v>
+        <v>-0.7074</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.901</v>
+        <v>-0.5795</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0397</v>
+        <v>-0.1278</v>
       </c>
       <c r="V14" t="n">
         <v>2.2289</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8984</v>
+        <v>2.3857</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1109</v>
+        <v>0.3177</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0092</v>
+        <v>2.068</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0961</v>
@@ -1624,13 +1624,13 @@
         <v>2.4974</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5077</v>
+        <v>-1.0204</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0315</v>
+        <v>-0.6029</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4762</v>
+        <v>-0.4175</v>
       </c>
       <c r="V15" t="n">
         <v>1.0048</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BIRD-JELINEK</t>
+          <t>A. INFANTE GUTIERREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3745</v>
+        <v>1.8323</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9853</v>
+        <v>0.9986</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3892</v>
+        <v>0.8337</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4486</v>
+        <v>2.8727</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0192</v>
+        <v>2.7592</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4678</v>
+        <v>0.1135</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0413</v>
+        <v>3.5383</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4501</v>
+        <v>2.6819</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4915</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4899</v>
+        <v>-0.6656</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4693</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9593</v>
+        <v>-0.7429</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8325</v>
+        <v>2.7055</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2612</v>
+        <v>-1.272</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9846</v>
+        <v>-0.4586</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2767</v>
+        <v>-0.8135</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.23</v>
+        <v>-0.3927</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.23</v>
+        <v>-0.3927</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. INFANTE GUTIERREZ</t>
+          <t>L. OBAJO BELTRAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2554</v>
+        <v>0.8423</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8914</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3639</v>
+        <v>1.6724</v>
       </c>
       <c r="G17" t="n">
-        <v>2.8727</v>
+        <v>2.2614</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7592</v>
+        <v>-1.0852</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1135</v>
+        <v>3.3465</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5383</v>
+        <v>1.2125</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6819</v>
+        <v>-1.4523</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8564000000000001</v>
+        <v>2.6648</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6656</v>
+        <v>1.0489</v>
       </c>
       <c r="N17" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.3672</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7429</v>
+        <v>0.6817</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7055</v>
+        <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8489</v>
+        <v>-1.6726</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5657</v>
+        <v>-1.002</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.2832</v>
+        <v>-0.6706</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3927</v>
+        <v>-0.1627</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3927</v>
+        <v>-0.1627</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. OBAJO BELTRAN</t>
+          <t>A. BIRD-JELINEK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6177</v>
+        <v>0.5173</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9373</v>
+        <v>0.128</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5549</v>
+        <v>0.3892</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2614</v>
+        <v>-0.4486</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0852</v>
+        <v>0.0192</v>
       </c>
       <c r="I18" t="n">
-        <v>3.3465</v>
+        <v>-0.4678</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2125</v>
+        <v>0.0413</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4523</v>
+        <v>-0.4501</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6648</v>
+        <v>0.4915</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0489</v>
+        <v>-0.4899</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3672</v>
+        <v>0.4693</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6817</v>
+        <v>-0.9593</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4162</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4568</v>
+        <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8972</v>
+        <v>1.404</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1091</v>
+        <v>1.1273</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.788</v>
+        <v>0.2767</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1627</v>
+        <v>-0.23</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1627</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. SALL</t>
+          <t>I. MONTERO MECA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2048</v>
+        <v>-0.1456</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1467</v>
+        <v>0.8729</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9419</v>
+        <v>-1.0185</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9046</v>
+        <v>1.2128</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6696</v>
+        <v>1.7443</v>
       </c>
       <c r="I19" t="n">
-        <v>0.765</v>
+        <v>-0.5315</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5657</v>
+        <v>2.9398</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.8981</v>
+        <v>2.3366</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3324</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.339</v>
+        <v>-1.727</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2284</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5674</v>
+        <v>-1.1348</v>
       </c>
       <c r="P19" t="n">
         <v>0.4162</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4568</v>
+        <v>2.4974</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6374</v>
+        <v>-0.7804</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2296</v>
+        <v>-0.3219</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4078</v>
+        <v>-0.4586</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3538</v>
+        <v>-0.9942</v>
       </c>
       <c r="W19" t="n">
-        <v>0.23</v>
+        <v>0.3361</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5838</v>
+        <v>-1.3303</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. MONTERO MECA</t>
+          <t>P. SALL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7489</v>
+        <v>-0.1666</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1228</v>
+        <v>-0.9324</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8717</v>
+        <v>0.7658</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2128</v>
+        <v>-0.9046</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7443</v>
+        <v>-1.6696</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5315</v>
+        <v>0.765</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9398</v>
+        <v>-0.5657</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3366</v>
+        <v>-1.8981</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6032999999999999</v>
+        <v>1.3324</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.727</v>
+        <v>-0.339</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.2284</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1348</v>
+        <v>-0.5674</v>
       </c>
       <c r="P20" t="n">
         <v>0.4162</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4974</v>
+        <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3837</v>
+        <v>0.6756</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.072</v>
+        <v>0.4439</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3118</v>
+        <v>0.2317</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9942</v>
+        <v>-0.3538</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3361</v>
+        <v>0.23</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3303</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5956</v>
+        <v>-1.5765</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7842</v>
+        <v>-0.677</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8114</v>
+        <v>-0.8995</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1571</v>
@@ -2092,13 +2092,13 @@
         <v>1.8731</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5651</v>
+        <v>-1.546</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0439</v>
+        <v>-0.9367</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5212</v>
+        <v>-0.6093</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7465000000000001</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1069</v>
+        <v>-6.4324</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5869</v>
+        <v>-4.7656</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.52</v>
+        <v>-1.6668</v>
       </c>
       <c r="G22" t="n">
         <v>-3.593</v>
@@ -2170,13 +2170,13 @@
         <v>1.6649</v>
       </c>
       <c r="S22" t="n">
-        <v>1.6943</v>
+        <v>0.3687</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5807</v>
+        <v>0.402</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1136</v>
+        <v>-0.0332</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7513</v>
@@ -2203,31 +2203,31 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.5406</v>
+        <v>2.5407</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0797</v>
+        <v>-3.079699999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>5.619999999999999</v>
+        <v>5.620200000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>3.285800000000001</v>
+        <v>3.285800000000002</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2658</v>
+        <v>-0.2657999999999996</v>
       </c>
       <c r="I23" t="n">
-        <v>3.551499999999999</v>
+        <v>3.5515</v>
       </c>
       <c r="J23" t="n">
-        <v>6.226500000000001</v>
+        <v>6.2265</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5732000000000004</v>
+        <v>0.5731999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>5.6536</v>
+        <v>5.653600000000001</v>
       </c>
       <c r="M23" t="n">
         <v>-2.9408</v>
@@ -2248,13 +2248,13 @@
         <v>16.6493</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.5504</v>
+        <v>-4.550500000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.9283</v>
+        <v>-1.9284</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.622</v>
+        <v>-2.6221</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3975</v>
@@ -2263,7 +2263,7 @@
         <v>4.0686</v>
       </c>
       <c r="X23" t="n">
-        <v>-5.466100000000001</v>
+        <v>-5.4661</v>
       </c>
     </row>
   </sheetData>
